--- a/files/temp_files/statement_2025_11.xlsx
+++ b/files/temp_files/statement_2025_11.xlsx
@@ -594,7 +594,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>107.97</v>
+        <v>-107.97</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>157.56</v>
+        <v>-157.56</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -622,7 +622,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>216.13</v>
+        <v>-216.13</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>102.91</v>
+        <v>-102.91</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -650,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>755.63</v>
+        <v>-755.63</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -664,7 +664,7 @@
         <v>39</v>
       </c>
       <c r="C7">
-        <v>349.15</v>
+        <v>-349.15</v>
       </c>
       <c r="D7" t="s">
         <v>62</v>
@@ -678,7 +678,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>120.44</v>
+        <v>-120.44</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -706,7 +706,7 @@
         <v>38</v>
       </c>
       <c r="C10">
-        <v>1.88</v>
+        <v>-1.88</v>
       </c>
       <c r="D10" t="s">
         <v>59</v>
@@ -734,7 +734,7 @@
         <v>43</v>
       </c>
       <c r="C12">
-        <v>13.7</v>
+        <v>-13.7</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>
@@ -762,7 +762,7 @@
         <v>44</v>
       </c>
       <c r="C14">
-        <v>164.63</v>
+        <v>-164.63</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -776,7 +776,7 @@
         <v>36</v>
       </c>
       <c r="C15">
-        <v>231.48</v>
+        <v>-231.48</v>
       </c>
       <c r="D15" t="s">
         <v>60</v>
@@ -790,7 +790,7 @@
         <v>45</v>
       </c>
       <c r="C16">
-        <v>36.55</v>
+        <v>-36.55</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -804,7 +804,7 @@
         <v>45</v>
       </c>
       <c r="C17">
-        <v>49.64</v>
+        <v>-49.64</v>
       </c>
       <c r="D17" t="s">
         <v>65</v>
@@ -832,7 +832,7 @@
         <v>39</v>
       </c>
       <c r="C19">
-        <v>190.41</v>
+        <v>-190.41</v>
       </c>
       <c r="D19" t="s">
         <v>62</v>
@@ -846,7 +846,7 @@
         <v>46</v>
       </c>
       <c r="C20">
-        <v>40.15</v>
+        <v>-40.15</v>
       </c>
       <c r="D20" t="s">
         <v>65</v>
@@ -860,7 +860,7 @@
         <v>43</v>
       </c>
       <c r="C21">
-        <v>59.76</v>
+        <v>-59.76</v>
       </c>
       <c r="D21" t="s">
         <v>64</v>
@@ -874,7 +874,7 @@
         <v>36</v>
       </c>
       <c r="C22">
-        <v>233.32</v>
+        <v>-233.32</v>
       </c>
       <c r="D22" t="s">
         <v>60</v>
@@ -888,7 +888,7 @@
         <v>47</v>
       </c>
       <c r="C23">
-        <v>117.63</v>
+        <v>-117.63</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -902,7 +902,7 @@
         <v>40</v>
       </c>
       <c r="C24">
-        <v>79.95</v>
+        <v>-79.95</v>
       </c>
       <c r="D24" t="s">
         <v>60</v>
@@ -916,7 +916,7 @@
         <v>40</v>
       </c>
       <c r="C25">
-        <v>138.4</v>
+        <v>-138.4</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -930,7 +930,7 @@
         <v>34</v>
       </c>
       <c r="C26">
-        <v>79.92</v>
+        <v>-79.92</v>
       </c>
       <c r="D26" t="s">
         <v>58</v>
@@ -944,7 +944,7 @@
         <v>48</v>
       </c>
       <c r="C27">
-        <v>157.75</v>
+        <v>-157.75</v>
       </c>
       <c r="D27" t="s">
         <v>60</v>
@@ -958,7 +958,7 @@
         <v>49</v>
       </c>
       <c r="C28">
-        <v>111.23</v>
+        <v>-111.23</v>
       </c>
       <c r="D28" t="s">
         <v>58</v>
@@ -972,7 +972,7 @@
         <v>50</v>
       </c>
       <c r="C29">
-        <v>165.46</v>
+        <v>-165.46</v>
       </c>
       <c r="D29" t="s">
         <v>61</v>
@@ -986,7 +986,7 @@
         <v>51</v>
       </c>
       <c r="C30">
-        <v>19</v>
+        <v>-19</v>
       </c>
       <c r="D30" t="s">
         <v>64</v>
@@ -1014,7 +1014,7 @@
         <v>34</v>
       </c>
       <c r="C32">
-        <v>123.69</v>
+        <v>-123.69</v>
       </c>
       <c r="D32" t="s">
         <v>58</v>
@@ -1028,7 +1028,7 @@
         <v>53</v>
       </c>
       <c r="C33">
-        <v>40.38</v>
+        <v>-40.38</v>
       </c>
       <c r="D33" t="s">
         <v>58</v>
@@ -1042,7 +1042,7 @@
         <v>54</v>
       </c>
       <c r="C34">
-        <v>4.74</v>
+        <v>-4.74</v>
       </c>
       <c r="D34" t="s">
         <v>65</v>
@@ -1056,7 +1056,7 @@
         <v>38</v>
       </c>
       <c r="C35">
-        <v>180.22</v>
+        <v>-180.22</v>
       </c>
       <c r="D35" t="s">
         <v>59</v>
@@ -1070,7 +1070,7 @@
         <v>53</v>
       </c>
       <c r="C36">
-        <v>133.6</v>
+        <v>-133.6</v>
       </c>
       <c r="D36" t="s">
         <v>58</v>
@@ -1084,7 +1084,7 @@
         <v>38</v>
       </c>
       <c r="C37">
-        <v>742.88</v>
+        <v>-742.88</v>
       </c>
       <c r="D37" t="s">
         <v>59</v>
@@ -1098,7 +1098,7 @@
         <v>55</v>
       </c>
       <c r="C38">
-        <v>100.56</v>
+        <v>-100.56</v>
       </c>
       <c r="D38" t="s">
         <v>62</v>
@@ -1112,7 +1112,7 @@
         <v>45</v>
       </c>
       <c r="C39">
-        <v>43.69</v>
+        <v>-43.69</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -1126,7 +1126,7 @@
         <v>50</v>
       </c>
       <c r="C40">
-        <v>106.66</v>
+        <v>-106.66</v>
       </c>
       <c r="D40" t="s">
         <v>61</v>
@@ -1140,7 +1140,7 @@
         <v>43</v>
       </c>
       <c r="C41">
-        <v>37.11</v>
+        <v>-37.11</v>
       </c>
       <c r="D41" t="s">
         <v>64</v>
@@ -1154,7 +1154,7 @@
         <v>35</v>
       </c>
       <c r="C42">
-        <v>768.23</v>
+        <v>-768.23</v>
       </c>
       <c r="D42" t="s">
         <v>59</v>
@@ -1168,7 +1168,7 @@
         <v>50</v>
       </c>
       <c r="C43">
-        <v>121.66</v>
+        <v>-121.66</v>
       </c>
       <c r="D43" t="s">
         <v>61</v>
@@ -1182,7 +1182,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>882.24</v>
+        <v>-882.24</v>
       </c>
       <c r="D44" t="s">
         <v>59</v>
@@ -1210,7 +1210,7 @@
         <v>44</v>
       </c>
       <c r="C46">
-        <v>132.65</v>
+        <v>-132.65</v>
       </c>
       <c r="D46" t="s">
         <v>61</v>
@@ -1224,7 +1224,7 @@
         <v>56</v>
       </c>
       <c r="C47">
-        <v>345.76</v>
+        <v>-345.76</v>
       </c>
       <c r="D47" t="s">
         <v>59</v>
@@ -1252,7 +1252,7 @@
         <v>44</v>
       </c>
       <c r="C49">
-        <v>106.61</v>
+        <v>-106.61</v>
       </c>
       <c r="D49" t="s">
         <v>61</v>
@@ -1266,7 +1266,7 @@
         <v>51</v>
       </c>
       <c r="C50">
-        <v>37.11</v>
+        <v>-37.11</v>
       </c>
       <c r="D50" t="s">
         <v>64</v>
@@ -1294,7 +1294,7 @@
         <v>53</v>
       </c>
       <c r="C52">
-        <v>84.95</v>
+        <v>-84.95</v>
       </c>
       <c r="D52" t="s">
         <v>58</v>
@@ -1308,7 +1308,7 @@
         <v>43</v>
       </c>
       <c r="C53">
-        <v>75.34</v>
+        <v>-75.34</v>
       </c>
       <c r="D53" t="s">
         <v>64</v>
@@ -1322,7 +1322,7 @@
         <v>43</v>
       </c>
       <c r="C54">
-        <v>99.14</v>
+        <v>-99.14</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
@@ -1336,7 +1336,7 @@
         <v>40</v>
       </c>
       <c r="C55">
-        <v>286.3</v>
+        <v>-286.3</v>
       </c>
       <c r="D55" t="s">
         <v>60</v>
@@ -1350,7 +1350,7 @@
         <v>54</v>
       </c>
       <c r="C56">
-        <v>30.34</v>
+        <v>-30.34</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -1364,7 +1364,7 @@
         <v>39</v>
       </c>
       <c r="C57">
-        <v>314.83</v>
+        <v>-314.83</v>
       </c>
       <c r="D57" t="s">
         <v>62</v>
@@ -1378,7 +1378,7 @@
         <v>44</v>
       </c>
       <c r="C58">
-        <v>164.25</v>
+        <v>-164.25</v>
       </c>
       <c r="D58" t="s">
         <v>61</v>
@@ -1392,7 +1392,7 @@
         <v>48</v>
       </c>
       <c r="C59">
-        <v>237.85</v>
+        <v>-237.85</v>
       </c>
       <c r="D59" t="s">
         <v>60</v>
@@ -1406,7 +1406,7 @@
         <v>35</v>
       </c>
       <c r="C60">
-        <v>213.7</v>
+        <v>-213.7</v>
       </c>
       <c r="D60" t="s">
         <v>59</v>
@@ -1434,7 +1434,7 @@
         <v>48</v>
       </c>
       <c r="C62">
-        <v>181.57</v>
+        <v>-181.57</v>
       </c>
       <c r="D62" t="s">
         <v>60</v>
@@ -1462,7 +1462,7 @@
         <v>34</v>
       </c>
       <c r="C64">
-        <v>109.32</v>
+        <v>-109.32</v>
       </c>
       <c r="D64" t="s">
         <v>58</v>
@@ -1476,7 +1476,7 @@
         <v>54</v>
       </c>
       <c r="C65">
-        <v>7.03</v>
+        <v>-7.03</v>
       </c>
       <c r="D65" t="s">
         <v>65</v>
@@ -1490,7 +1490,7 @@
         <v>45</v>
       </c>
       <c r="C66">
-        <v>47.34</v>
+        <v>-47.34</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -1504,7 +1504,7 @@
         <v>50</v>
       </c>
       <c r="C67">
-        <v>113.24</v>
+        <v>-113.24</v>
       </c>
       <c r="D67" t="s">
         <v>61</v>
@@ -1532,7 +1532,7 @@
         <v>56</v>
       </c>
       <c r="C69">
-        <v>826.8099999999999</v>
+        <v>-826.8099999999999</v>
       </c>
       <c r="D69" t="s">
         <v>59</v>
@@ -1546,7 +1546,7 @@
         <v>49</v>
       </c>
       <c r="C70">
-        <v>77.64</v>
+        <v>-77.64</v>
       </c>
       <c r="D70" t="s">
         <v>58</v>
@@ -1560,7 +1560,7 @@
         <v>54</v>
       </c>
       <c r="C71">
-        <v>5.47</v>
+        <v>-5.47</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -1574,7 +1574,7 @@
         <v>54</v>
       </c>
       <c r="C72">
-        <v>30.03</v>
+        <v>-30.03</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -1602,7 +1602,7 @@
         <v>38</v>
       </c>
       <c r="C74">
-        <v>893.37</v>
+        <v>-893.37</v>
       </c>
       <c r="D74" t="s">
         <v>59</v>
@@ -1616,7 +1616,7 @@
         <v>54</v>
       </c>
       <c r="C75">
-        <v>32.91</v>
+        <v>-32.91</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -1644,7 +1644,7 @@
         <v>46</v>
       </c>
       <c r="C77">
-        <v>17.29</v>
+        <v>-17.29</v>
       </c>
       <c r="D77" t="s">
         <v>65</v>
@@ -1658,7 +1658,7 @@
         <v>57</v>
       </c>
       <c r="C78">
-        <v>76.5</v>
+        <v>-76.5</v>
       </c>
       <c r="D78" t="s">
         <v>64</v>
@@ -1672,7 +1672,7 @@
         <v>47</v>
       </c>
       <c r="C79">
-        <v>134.79</v>
+        <v>-134.79</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1686,7 +1686,7 @@
         <v>39</v>
       </c>
       <c r="C80">
-        <v>261.08</v>
+        <v>-261.08</v>
       </c>
       <c r="D80" t="s">
         <v>62</v>
@@ -1714,7 +1714,7 @@
         <v>35</v>
       </c>
       <c r="C82">
-        <v>110.82</v>
+        <v>-110.82</v>
       </c>
       <c r="D82" t="s">
         <v>59</v>
@@ -1742,7 +1742,7 @@
         <v>39</v>
       </c>
       <c r="C84">
-        <v>234.94</v>
+        <v>-234.94</v>
       </c>
       <c r="D84" t="s">
         <v>62</v>
@@ -1756,7 +1756,7 @@
         <v>46</v>
       </c>
       <c r="C85">
-        <v>17.96</v>
+        <v>-17.96</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -1770,7 +1770,7 @@
         <v>47</v>
       </c>
       <c r="C86">
-        <v>62.57</v>
+        <v>-62.57</v>
       </c>
       <c r="D86" t="s">
         <v>62</v>
@@ -1798,7 +1798,7 @@
         <v>54</v>
       </c>
       <c r="C88">
-        <v>9.57</v>
+        <v>-9.57</v>
       </c>
       <c r="D88" t="s">
         <v>65</v>
@@ -1812,7 +1812,7 @@
         <v>56</v>
       </c>
       <c r="C89">
-        <v>579.5599999999999</v>
+        <v>-579.5599999999999</v>
       </c>
       <c r="D89" t="s">
         <v>59</v>
@@ -1826,7 +1826,7 @@
         <v>44</v>
       </c>
       <c r="C90">
-        <v>17.37</v>
+        <v>-17.37</v>
       </c>
       <c r="D90" t="s">
         <v>61</v>
@@ -1840,7 +1840,7 @@
         <v>54</v>
       </c>
       <c r="C91">
-        <v>31.68</v>
+        <v>-31.68</v>
       </c>
       <c r="D91" t="s">
         <v>65</v>
@@ -1854,7 +1854,7 @@
         <v>54</v>
       </c>
       <c r="C92">
-        <v>13.2</v>
+        <v>-13.2</v>
       </c>
       <c r="D92" t="s">
         <v>65</v>
@@ -1868,7 +1868,7 @@
         <v>53</v>
       </c>
       <c r="C93">
-        <v>70.09999999999999</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="D93" t="s">
         <v>58</v>
@@ -1882,7 +1882,7 @@
         <v>57</v>
       </c>
       <c r="C94">
-        <v>78</v>
+        <v>-78</v>
       </c>
       <c r="D94" t="s">
         <v>64</v>
@@ -1924,7 +1924,7 @@
         <v>56</v>
       </c>
       <c r="C97">
-        <v>621.7</v>
+        <v>-621.7</v>
       </c>
       <c r="D97" t="s">
         <v>59</v>
@@ -1938,7 +1938,7 @@
         <v>43</v>
       </c>
       <c r="C98">
-        <v>39.45</v>
+        <v>-39.45</v>
       </c>
       <c r="D98" t="s">
         <v>64</v>
@@ -1952,7 +1952,7 @@
         <v>43</v>
       </c>
       <c r="C99">
-        <v>48.78</v>
+        <v>-48.78</v>
       </c>
       <c r="D99" t="s">
         <v>64</v>
@@ -1966,7 +1966,7 @@
         <v>51</v>
       </c>
       <c r="C100">
-        <v>35.38</v>
+        <v>-35.38</v>
       </c>
       <c r="D100" t="s">
         <v>64</v>
@@ -1980,7 +1980,7 @@
         <v>35</v>
       </c>
       <c r="C101">
-        <v>897.75</v>
+        <v>-897.75</v>
       </c>
       <c r="D101" t="s">
         <v>59</v>
@@ -1994,7 +1994,7 @@
         <v>50</v>
       </c>
       <c r="C102">
-        <v>150.73</v>
+        <v>-150.73</v>
       </c>
       <c r="D102" t="s">
         <v>61</v>
@@ -2008,7 +2008,7 @@
         <v>46</v>
       </c>
       <c r="C103">
-        <v>27.81</v>
+        <v>-27.81</v>
       </c>
       <c r="D103" t="s">
         <v>65</v>
@@ -2022,7 +2022,7 @@
         <v>57</v>
       </c>
       <c r="C104">
-        <v>88.40000000000001</v>
+        <v>-88.40000000000001</v>
       </c>
       <c r="D104" t="s">
         <v>64</v>
@@ -2036,7 +2036,7 @@
         <v>55</v>
       </c>
       <c r="C105">
-        <v>443.93</v>
+        <v>-443.93</v>
       </c>
       <c r="D105" t="s">
         <v>62</v>
@@ -2050,7 +2050,7 @@
         <v>55</v>
       </c>
       <c r="C106">
-        <v>117.97</v>
+        <v>-117.97</v>
       </c>
       <c r="D106" t="s">
         <v>62</v>
@@ -2064,7 +2064,7 @@
         <v>46</v>
       </c>
       <c r="C107">
-        <v>37.99</v>
+        <v>-37.99</v>
       </c>
       <c r="D107" t="s">
         <v>65</v>
@@ -2078,7 +2078,7 @@
         <v>44</v>
       </c>
       <c r="C108">
-        <v>22.47</v>
+        <v>-22.47</v>
       </c>
       <c r="D108" t="s">
         <v>61</v>
@@ -2106,7 +2106,7 @@
         <v>34</v>
       </c>
       <c r="C110">
-        <v>22.57</v>
+        <v>-22.57</v>
       </c>
       <c r="D110" t="s">
         <v>58</v>
@@ -2120,7 +2120,7 @@
         <v>55</v>
       </c>
       <c r="C111">
-        <v>122.71</v>
+        <v>-122.71</v>
       </c>
       <c r="D111" t="s">
         <v>62</v>
@@ -2134,7 +2134,7 @@
         <v>34</v>
       </c>
       <c r="C112">
-        <v>101.55</v>
+        <v>-101.55</v>
       </c>
       <c r="D112" t="s">
         <v>58</v>
@@ -2148,7 +2148,7 @@
         <v>39</v>
       </c>
       <c r="C113">
-        <v>95.36</v>
+        <v>-95.36</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2162,7 +2162,7 @@
         <v>44</v>
       </c>
       <c r="C114">
-        <v>116</v>
+        <v>-116</v>
       </c>
       <c r="D114" t="s">
         <v>61</v>
@@ -2176,7 +2176,7 @@
         <v>51</v>
       </c>
       <c r="C115">
-        <v>89.47</v>
+        <v>-89.47</v>
       </c>
       <c r="D115" t="s">
         <v>64</v>
@@ -2190,7 +2190,7 @@
         <v>38</v>
       </c>
       <c r="C116">
-        <v>976.98</v>
+        <v>-976.98</v>
       </c>
       <c r="D116" t="s">
         <v>59</v>
@@ -2204,7 +2204,7 @@
         <v>54</v>
       </c>
       <c r="C117">
-        <v>39.16</v>
+        <v>-39.16</v>
       </c>
       <c r="D117" t="s">
         <v>65</v>
@@ -2218,7 +2218,7 @@
         <v>36</v>
       </c>
       <c r="C118">
-        <v>70.55</v>
+        <v>-70.55</v>
       </c>
       <c r="D118" t="s">
         <v>60</v>
@@ -2232,7 +2232,7 @@
         <v>57</v>
       </c>
       <c r="C119">
-        <v>91.67</v>
+        <v>-91.67</v>
       </c>
       <c r="D119" t="s">
         <v>64</v>
@@ -2246,7 +2246,7 @@
         <v>51</v>
       </c>
       <c r="C120">
-        <v>45.19</v>
+        <v>-45.19</v>
       </c>
       <c r="D120" t="s">
         <v>64</v>
@@ -2274,7 +2274,7 @@
         <v>34</v>
       </c>
       <c r="C122">
-        <v>32.8</v>
+        <v>-32.8</v>
       </c>
       <c r="D122" t="s">
         <v>58</v>
@@ -2288,7 +2288,7 @@
         <v>51</v>
       </c>
       <c r="C123">
-        <v>85.7</v>
+        <v>-85.7</v>
       </c>
       <c r="D123" t="s">
         <v>64</v>
@@ -2302,7 +2302,7 @@
         <v>53</v>
       </c>
       <c r="C124">
-        <v>125.95</v>
+        <v>-125.95</v>
       </c>
       <c r="D124" t="s">
         <v>58</v>
@@ -2316,7 +2316,7 @@
         <v>53</v>
       </c>
       <c r="C125">
-        <v>112.4</v>
+        <v>-112.4</v>
       </c>
       <c r="D125" t="s">
         <v>58</v>
@@ -2330,7 +2330,7 @@
         <v>48</v>
       </c>
       <c r="C126">
-        <v>183.23</v>
+        <v>-183.23</v>
       </c>
       <c r="D126" t="s">
         <v>60</v>
@@ -2344,7 +2344,7 @@
         <v>48</v>
       </c>
       <c r="C127">
-        <v>84.94</v>
+        <v>-84.94</v>
       </c>
       <c r="D127" t="s">
         <v>60</v>
@@ -2358,7 +2358,7 @@
         <v>40</v>
       </c>
       <c r="C128">
-        <v>195.2</v>
+        <v>-195.2</v>
       </c>
       <c r="D128" t="s">
         <v>60</v>
@@ -2386,7 +2386,7 @@
         <v>38</v>
       </c>
       <c r="C130">
-        <v>658.71</v>
+        <v>-658.71</v>
       </c>
       <c r="D130" t="s">
         <v>59</v>
@@ -2400,7 +2400,7 @@
         <v>36</v>
       </c>
       <c r="C131">
-        <v>93.31999999999999</v>
+        <v>-93.31999999999999</v>
       </c>
       <c r="D131" t="s">
         <v>60</v>
@@ -2414,7 +2414,7 @@
         <v>35</v>
       </c>
       <c r="C132">
-        <v>50.98</v>
+        <v>-50.98</v>
       </c>
       <c r="D132" t="s">
         <v>59</v>
@@ -2442,7 +2442,7 @@
         <v>45</v>
       </c>
       <c r="C134">
-        <v>1.08</v>
+        <v>-1.08</v>
       </c>
       <c r="D134" t="s">
         <v>65</v>
@@ -2456,7 +2456,7 @@
         <v>40</v>
       </c>
       <c r="C135">
-        <v>62.51</v>
+        <v>-62.51</v>
       </c>
       <c r="D135" t="s">
         <v>60</v>
@@ -2484,7 +2484,7 @@
         <v>35</v>
       </c>
       <c r="C137">
-        <v>286.51</v>
+        <v>-286.51</v>
       </c>
       <c r="D137" t="s">
         <v>59</v>
@@ -2498,7 +2498,7 @@
         <v>46</v>
       </c>
       <c r="C138">
-        <v>21.39</v>
+        <v>-21.39</v>
       </c>
       <c r="D138" t="s">
         <v>65</v>
@@ -2512,7 +2512,7 @@
         <v>36</v>
       </c>
       <c r="C139">
-        <v>289.01</v>
+        <v>-289.01</v>
       </c>
       <c r="D139" t="s">
         <v>60</v>
@@ -2526,7 +2526,7 @@
         <v>50</v>
       </c>
       <c r="C140">
-        <v>40.24</v>
+        <v>-40.24</v>
       </c>
       <c r="D140" t="s">
         <v>61</v>
@@ -2540,7 +2540,7 @@
         <v>53</v>
       </c>
       <c r="C141">
-        <v>130.68</v>
+        <v>-130.68</v>
       </c>
       <c r="D141" t="s">
         <v>58</v>
@@ -2554,7 +2554,7 @@
         <v>54</v>
       </c>
       <c r="C142">
-        <v>12.61</v>
+        <v>-12.61</v>
       </c>
       <c r="D142" t="s">
         <v>65</v>
@@ -2568,7 +2568,7 @@
         <v>45</v>
       </c>
       <c r="C143">
-        <v>24.79</v>
+        <v>-24.79</v>
       </c>
       <c r="D143" t="s">
         <v>65</v>
@@ -2582,7 +2582,7 @@
         <v>45</v>
       </c>
       <c r="C144">
-        <v>20.15</v>
+        <v>-20.15</v>
       </c>
       <c r="D144" t="s">
         <v>65</v>
@@ -2596,7 +2596,7 @@
         <v>37</v>
       </c>
       <c r="C145">
-        <v>152.21</v>
+        <v>-152.21</v>
       </c>
       <c r="D145" t="s">
         <v>61</v>
@@ -2610,7 +2610,7 @@
         <v>51</v>
       </c>
       <c r="C146">
-        <v>94</v>
+        <v>-94</v>
       </c>
       <c r="D146" t="s">
         <v>64</v>
@@ -2624,7 +2624,7 @@
         <v>38</v>
       </c>
       <c r="C147">
-        <v>872.73</v>
+        <v>-872.73</v>
       </c>
       <c r="D147" t="s">
         <v>59</v>
@@ -2638,7 +2638,7 @@
         <v>40</v>
       </c>
       <c r="C148">
-        <v>220.9</v>
+        <v>-220.9</v>
       </c>
       <c r="D148" t="s">
         <v>60</v>
@@ -2652,7 +2652,7 @@
         <v>39</v>
       </c>
       <c r="C149">
-        <v>460.61</v>
+        <v>-460.61</v>
       </c>
       <c r="D149" t="s">
         <v>62</v>
@@ -2666,7 +2666,7 @@
         <v>45</v>
       </c>
       <c r="C150">
-        <v>27.77</v>
+        <v>-27.77</v>
       </c>
       <c r="D150" t="s">
         <v>65</v>
@@ -2680,7 +2680,7 @@
         <v>37</v>
       </c>
       <c r="C151">
-        <v>183.81</v>
+        <v>-183.81</v>
       </c>
       <c r="D151" t="s">
         <v>61</v>
@@ -2694,7 +2694,7 @@
         <v>44</v>
       </c>
       <c r="C152">
-        <v>147</v>
+        <v>-147</v>
       </c>
       <c r="D152" t="s">
         <v>61</v>
@@ -2708,7 +2708,7 @@
         <v>49</v>
       </c>
       <c r="C153">
-        <v>54.76</v>
+        <v>-54.76</v>
       </c>
       <c r="D153" t="s">
         <v>58</v>
@@ -2722,7 +2722,7 @@
         <v>40</v>
       </c>
       <c r="C154">
-        <v>58.63</v>
+        <v>-58.63</v>
       </c>
       <c r="D154" t="s">
         <v>60</v>
@@ -2736,7 +2736,7 @@
         <v>45</v>
       </c>
       <c r="C155">
-        <v>32.66</v>
+        <v>-32.66</v>
       </c>
       <c r="D155" t="s">
         <v>65</v>
@@ -2750,7 +2750,7 @@
         <v>46</v>
       </c>
       <c r="C156">
-        <v>29.72</v>
+        <v>-29.72</v>
       </c>
       <c r="D156" t="s">
         <v>65</v>
@@ -2764,7 +2764,7 @@
         <v>37</v>
       </c>
       <c r="C157">
-        <v>169.04</v>
+        <v>-169.04</v>
       </c>
       <c r="D157" t="s">
         <v>61</v>
@@ -2778,7 +2778,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>184.22</v>
+        <v>-184.22</v>
       </c>
       <c r="D158" t="s">
         <v>61</v>
@@ -2792,7 +2792,7 @@
         <v>36</v>
       </c>
       <c r="C159">
-        <v>249.59</v>
+        <v>-249.59</v>
       </c>
       <c r="D159" t="s">
         <v>60</v>
@@ -2806,7 +2806,7 @@
         <v>44</v>
       </c>
       <c r="C160">
-        <v>134.36</v>
+        <v>-134.36</v>
       </c>
       <c r="D160" t="s">
         <v>61</v>
@@ -2820,7 +2820,7 @@
         <v>40</v>
       </c>
       <c r="C161">
-        <v>69.97</v>
+        <v>-69.97</v>
       </c>
       <c r="D161" t="s">
         <v>60</v>
@@ -2848,7 +2848,7 @@
         <v>35</v>
       </c>
       <c r="C163">
-        <v>402.74</v>
+        <v>-402.74</v>
       </c>
       <c r="D163" t="s">
         <v>59</v>
@@ -2862,7 +2862,7 @@
         <v>40</v>
       </c>
       <c r="C164">
-        <v>230.28</v>
+        <v>-230.28</v>
       </c>
       <c r="D164" t="s">
         <v>60</v>
@@ -2876,7 +2876,7 @@
         <v>47</v>
       </c>
       <c r="C165">
-        <v>126.87</v>
+        <v>-126.87</v>
       </c>
       <c r="D165" t="s">
         <v>62</v>
@@ -2890,7 +2890,7 @@
         <v>43</v>
       </c>
       <c r="C166">
-        <v>91.01000000000001</v>
+        <v>-91.01000000000001</v>
       </c>
       <c r="D166" t="s">
         <v>64</v>
@@ -2904,7 +2904,7 @@
         <v>35</v>
       </c>
       <c r="C167">
-        <v>744.24</v>
+        <v>-744.24</v>
       </c>
       <c r="D167" t="s">
         <v>59</v>
@@ -2918,7 +2918,7 @@
         <v>36</v>
       </c>
       <c r="C168">
-        <v>185.44</v>
+        <v>-185.44</v>
       </c>
       <c r="D168" t="s">
         <v>60</v>
@@ -2932,7 +2932,7 @@
         <v>49</v>
       </c>
       <c r="C169">
-        <v>84.79000000000001</v>
+        <v>-84.79000000000001</v>
       </c>
       <c r="D169" t="s">
         <v>58</v>
@@ -2946,7 +2946,7 @@
         <v>56</v>
       </c>
       <c r="C170">
-        <v>440.88</v>
+        <v>-440.88</v>
       </c>
       <c r="D170" t="s">
         <v>59</v>
@@ -2960,7 +2960,7 @@
         <v>49</v>
       </c>
       <c r="C171">
-        <v>79.2</v>
+        <v>-79.2</v>
       </c>
       <c r="D171" t="s">
         <v>58</v>
@@ -2988,7 +2988,7 @@
         <v>54</v>
       </c>
       <c r="C173">
-        <v>32.37</v>
+        <v>-32.37</v>
       </c>
       <c r="D173" t="s">
         <v>65</v>
@@ -3016,7 +3016,7 @@
         <v>40</v>
       </c>
       <c r="C175">
-        <v>155.99</v>
+        <v>-155.99</v>
       </c>
       <c r="D175" t="s">
         <v>60</v>
@@ -3030,7 +3030,7 @@
         <v>38</v>
       </c>
       <c r="C176">
-        <v>630.99</v>
+        <v>-630.99</v>
       </c>
       <c r="D176" t="s">
         <v>59</v>
@@ -3044,7 +3044,7 @@
         <v>36</v>
       </c>
       <c r="C177">
-        <v>41.63</v>
+        <v>-41.63</v>
       </c>
       <c r="D177" t="s">
         <v>60</v>
@@ -3058,7 +3058,7 @@
         <v>39</v>
       </c>
       <c r="C178">
-        <v>50.52</v>
+        <v>-50.52</v>
       </c>
       <c r="D178" t="s">
         <v>62</v>
@@ -3072,7 +3072,7 @@
         <v>56</v>
       </c>
       <c r="C179">
-        <v>539.5700000000001</v>
+        <v>-539.5700000000001</v>
       </c>
       <c r="D179" t="s">
         <v>59</v>
@@ -3086,7 +3086,7 @@
         <v>43</v>
       </c>
       <c r="C180">
-        <v>17.69</v>
+        <v>-17.69</v>
       </c>
       <c r="D180" t="s">
         <v>64</v>
@@ -3100,7 +3100,7 @@
         <v>55</v>
       </c>
       <c r="C181">
-        <v>218.39</v>
+        <v>-218.39</v>
       </c>
       <c r="D181" t="s">
         <v>62</v>
@@ -3114,7 +3114,7 @@
         <v>35</v>
       </c>
       <c r="C182">
-        <v>93.03</v>
+        <v>-93.03</v>
       </c>
       <c r="D182" t="s">
         <v>59</v>
@@ -3128,7 +3128,7 @@
         <v>35</v>
       </c>
       <c r="C183">
-        <v>648.5700000000001</v>
+        <v>-648.5700000000001</v>
       </c>
       <c r="D183" t="s">
         <v>59</v>
@@ -3156,7 +3156,7 @@
         <v>55</v>
       </c>
       <c r="C185">
-        <v>134.41</v>
+        <v>-134.41</v>
       </c>
       <c r="D185" t="s">
         <v>62</v>
@@ -3170,7 +3170,7 @@
         <v>39</v>
       </c>
       <c r="C186">
-        <v>212.94</v>
+        <v>-212.94</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -3184,7 +3184,7 @@
         <v>44</v>
       </c>
       <c r="C187">
-        <v>192.16</v>
+        <v>-192.16</v>
       </c>
       <c r="D187" t="s">
         <v>61</v>
@@ -3198,7 +3198,7 @@
         <v>50</v>
       </c>
       <c r="C188">
-        <v>71.34</v>
+        <v>-71.34</v>
       </c>
       <c r="D188" t="s">
         <v>61</v>
@@ -3212,7 +3212,7 @@
         <v>46</v>
       </c>
       <c r="C189">
-        <v>29.5</v>
+        <v>-29.5</v>
       </c>
       <c r="D189" t="s">
         <v>65</v>
@@ -3240,7 +3240,7 @@
         <v>37</v>
       </c>
       <c r="C191">
-        <v>160.27</v>
+        <v>-160.27</v>
       </c>
       <c r="D191" t="s">
         <v>61</v>
@@ -3254,7 +3254,7 @@
         <v>57</v>
       </c>
       <c r="C192">
-        <v>74.56999999999999</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="D192" t="s">
         <v>64</v>
@@ -3268,7 +3268,7 @@
         <v>54</v>
       </c>
       <c r="C193">
-        <v>27.13</v>
+        <v>-27.13</v>
       </c>
       <c r="D193" t="s">
         <v>65</v>
@@ -3282,7 +3282,7 @@
         <v>36</v>
       </c>
       <c r="C194">
-        <v>241.24</v>
+        <v>-241.24</v>
       </c>
       <c r="D194" t="s">
         <v>60</v>
@@ -3296,7 +3296,7 @@
         <v>36</v>
       </c>
       <c r="C195">
-        <v>235.11</v>
+        <v>-235.11</v>
       </c>
       <c r="D195" t="s">
         <v>60</v>
@@ -3310,7 +3310,7 @@
         <v>43</v>
       </c>
       <c r="C196">
-        <v>30.54</v>
+        <v>-30.54</v>
       </c>
       <c r="D196" t="s">
         <v>64</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="C197">
-        <v>162.68</v>
+        <v>-162.68</v>
       </c>
       <c r="D197" t="s">
         <v>60</v>
@@ -3352,7 +3352,7 @@
         <v>48</v>
       </c>
       <c r="C199">
-        <v>249.93</v>
+        <v>-249.93</v>
       </c>
       <c r="D199" t="s">
         <v>60</v>
@@ -3366,7 +3366,7 @@
         <v>54</v>
       </c>
       <c r="C200">
-        <v>1.44</v>
+        <v>-1.44</v>
       </c>
       <c r="D200" t="s">
         <v>65</v>
